--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,496 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128862493</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522279</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7036237</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128862489</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96865</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522120</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036143</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128862494</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522137</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036124</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128862496</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91655</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522187</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7036138</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128862497</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91755</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522128</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7036120</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128862494</v>
       </c>
       <c r="B6" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91655</v>
+        <v>91660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91755</v>
+        <v>91760</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128862494</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128862493</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128862494</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128862493</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128862494</v>
       </c>
       <c r="B6" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>128862489</v>
       </c>
       <c r="B5" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128862494</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>128862496</v>
       </c>
       <c r="B7" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>128862497</v>
       </c>
       <c r="B8" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128862493</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128862493</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128862493</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>128862493</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89046621</v>
+        <v>89046649</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skårelflyn, V om, Jmt</t>
+          <t>Ruvens östsida, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522306.9744895889</v>
+        <v>522540</v>
       </c>
       <c r="R2" t="n">
-        <v>7036199.944011324</v>
+        <v>7036133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre granskog med örtinslag i blockig svacka</t>
+          <t>i mindre lok med gyttjig botten</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2 substratenheter # tidvis dränkta gamla lågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,50 +789,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89046625</v>
+        <v>128862489</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skårelflyn, V om, Jmt</t>
+          <t>Ruven, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522370.885324702</v>
+        <v>522120</v>
       </c>
       <c r="R3" t="n">
-        <v>7036284.940542147</v>
+        <v>7036143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,57 +870,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>kalkpåverkad örtrik granskog i svacka</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128862493</v>
+        <v>128862497</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522279</v>
+        <v>522128</v>
       </c>
       <c r="R4" t="n">
-        <v>7036237</v>
+        <v>7036120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,11 +957,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,45 +983,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128862489</v>
+        <v>89046625</v>
       </c>
       <c r="B5" t="n">
-        <v>96956</v>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522120</v>
+        <v>522371</v>
       </c>
       <c r="R5" t="n">
-        <v>7036143</v>
+        <v>7036285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,61 +1064,70 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>kalkpåverkad örtrik granskog i svacka</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128862494</v>
+        <v>89046650</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Ruvens östsida, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522137</v>
+        <v>522542</v>
       </c>
       <c r="R6" t="n">
-        <v>7036124</v>
+        <v>7036104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,12 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,61 +1170,70 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog i örtrik friskmarkssvacka</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128862496</v>
+        <v>89046654</v>
       </c>
       <c r="B7" t="n">
-        <v>91716</v>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Ruvens östsida, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522187</v>
+        <v>522454</v>
       </c>
       <c r="R7" t="n">
-        <v>7036138</v>
+        <v>7035994</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,12 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,61 +1276,70 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre kalkgranskog i örtrik moränsvacka</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128862497</v>
+        <v>89046622</v>
       </c>
       <c r="B8" t="n">
-        <v>91816</v>
+        <v>81312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522128</v>
+        <v>522254</v>
       </c>
       <c r="R8" t="n">
-        <v>7036120</v>
+        <v>7036104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1366,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,19 +1382,1313 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>gammal tallskog på blockig moränhöjd</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # mkt grov och hög brandstubbe, 60 cm bred, 5 m hög</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>89046655</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>522489</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7035975</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkpåverkad barrnaturskog i anslutning till lok</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga, förrötad</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>89046624</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97518</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mikroskapania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scapania carinthiaca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>J.B.Jack ex Lindb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skårelflyn, V om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>522475</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7036260</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>i lok med dyig botten omgiven av gammal granskog</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>3 substratenheter # tidvis dränkta, grova gamla tallågor med svart ytved</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128862496</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>522187</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7036138</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128862490</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>522460</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7036289</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89046648</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87412</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>522496</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7036165</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>gammal kalkgranskog i örtrik friskmarkssvacka</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128862494</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>522137</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7036124</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128862493</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>522279</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7036237</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89046621</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skårelflyn, V om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>522307</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7036200</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>äldre granskog med örtinslag i blockig svacka</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89046651</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>522568</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7036052</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>olikåldrig barrblandskog i örtrik och något fuktig svacka</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>kanten av tuvor</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89046652</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>522568</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7036052</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>olikåldrig barrblandskog i örtrik och något fuktig svacka</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89046620</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skårelflyn, V om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>522277</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7036328</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>äldre granskog i örtrik svacka</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89046653</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ruvens östsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>522454</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7035994</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>äldre kalkgranskog i örtrik moränsvacka</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32304-2025 artfynd.xlsx
+++ b/artfynd/A 32304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046649</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046625</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046654</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046622</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046655</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046624</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862496</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862490</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046648</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862494</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862493</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2250,6 +2325,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046621</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046651</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046652</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046620</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2689,8 +2784,34 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046653</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>